--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488300_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488300_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.192</v>
+        <v>11.052</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3922</v>
+        <v>7.0552</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7998</v>
+        <v>3.9968</v>
       </c>
       <c r="G2" t="n">
         <v>4.7448</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1883</v>
+        <v>1.0483</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5944</v>
+        <v>0.2574</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5939</v>
+        <v>0.7909</v>
       </c>
       <c r="V2" t="n">
         <v>3.7766</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.1235</v>
+        <v>7.7383</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4094</v>
+        <v>5.8765</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7141</v>
+        <v>1.8618</v>
       </c>
       <c r="G3" t="n">
         <v>6.5791</v>
@@ -688,13 +688,13 @@
         <v>0.7411</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2861</v>
+        <v>0.9009</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8133</v>
+        <v>0.2804</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4728</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.6289</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>M. ORTEGA CARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5929</v>
+        <v>3.7604</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0756</v>
+        <v>0.2047</v>
       </c>
       <c r="F4" t="n">
-        <v>4.6685</v>
+        <v>3.5557</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4289</v>
+        <v>2.9288</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1431</v>
+        <v>0.6708</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2858</v>
+        <v>2.2579</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2901</v>
+        <v>1.8663</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2581</v>
+        <v>1.1293</v>
       </c>
       <c r="L4" t="n">
-        <v>0.032</v>
+        <v>0.7371</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1388</v>
+        <v>1.0625</v>
       </c>
       <c r="N4" t="n">
-        <v>0.885</v>
+        <v>-0.4584</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2537</v>
+        <v>1.5209</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.891</v>
+        <v>-1.1117</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>4.0731</v>
+        <v>0.0905</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8964</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1766</v>
+        <v>0.6404</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LAGHRIDAT</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9829</v>
+        <v>2.3662</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2234</v>
+        <v>-1.4898</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7595</v>
+        <v>3.856</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.36</v>
+        <v>2.4289</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6934</v>
+        <v>2.1431</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3334</v>
+        <v>0.2858</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.2937</v>
+        <v>1.2901</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8897</v>
+        <v>1.2581</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.404</v>
+        <v>0.032</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0663</v>
+        <v>1.1388</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8037</v>
+        <v>0.885</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.2537</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6676</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.891</v>
       </c>
       <c r="R5" t="n">
         <v>1.6676</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6753</v>
+        <v>1.8463</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5171</v>
+        <v>0.4822</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1582</v>
+        <v>1.3641</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ORTEGA CARO</t>
+          <t>S. LAGHRIDAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9452</v>
+        <v>1.5353</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3397</v>
+        <v>-0.658</v>
       </c>
       <c r="F6" t="n">
-        <v>3.2849</v>
+        <v>2.1932</v>
       </c>
       <c r="G6" t="n">
-        <v>2.9288</v>
+        <v>-1.36</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6708</v>
+        <v>-1.6934</v>
       </c>
       <c r="I6" t="n">
-        <v>2.2579</v>
+        <v>0.3334</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8663</v>
+        <v>-1.2937</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1293</v>
+        <v>-0.8897</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7371</v>
+        <v>-0.404</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0625</v>
+        <v>-0.0663</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4584</v>
+        <v>-0.8037</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5209</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7411</v>
+        <v>1.6676</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7247</v>
+        <v>1.2277</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0943</v>
+        <v>0.6358</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3696</v>
+        <v>0.5919</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6594</v>
+        <v>1.4641</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1233</v>
+        <v>0.8295</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5361</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>0.3656</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2932</v>
+        <v>0.0979</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1604</v>
+        <v>-0.1334</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1328</v>
+        <v>0.2313</v>
       </c>
       <c r="V7" t="n">
         <v>0.63</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1123</v>
+        <v>1.1369</v>
       </c>
       <c r="E8" t="n">
         <v>0.2683</v>
       </c>
       <c r="F8" t="n">
-        <v>0.844</v>
+        <v>0.8686</v>
       </c>
       <c r="G8" t="n">
         <v>0.8771</v>
@@ -1078,13 +1078,13 @@
         <v>0.1853</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05</v>
+        <v>0.0746</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1094</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1594</v>
+        <v>0.184</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2957</v>
+        <v>0.4921</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3484</v>
+        <v>-0.2505</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6441</v>
+        <v>0.7426</v>
       </c>
       <c r="G9" t="n">
         <v>0.8939</v>
@@ -1156,13 +1156,13 @@
         <v>0.1853</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4691</v>
+        <v>-0.2726</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1408</v>
+        <v>-0.0423</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3144</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1545</v>
+        <v>-0.9878</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0378</v>
+        <v>-1.4754</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8833</v>
+        <v>0.4877</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8445</v>
+        <v>-1.9982</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9157</v>
+        <v>-1.1577</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7603</v>
+        <v>-0.8405</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7383</v>
+        <v>-1.7319</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1375</v>
+        <v>-1.091</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6007</v>
+        <v>-0.6409</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1063</v>
+        <v>-0.2663</v>
       </c>
       <c r="N10" t="n">
-        <v>1.0533</v>
+        <v>-0.0667</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1596</v>
+        <v>-0.1996</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1853</v>
+        <v>1.1117</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2353</v>
+        <v>0.5276</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1131</v>
+        <v>0.2565</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1221</v>
+        <v>0.2711</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.26</v>
+        <v>-0.6289</v>
       </c>
       <c r="W10" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3112</v>
+        <v>-1.4432</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5527</v>
+        <v>-2.5481</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2414</v>
+        <v>1.1049</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.9982</v>
+        <v>-0.8445</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1577</v>
+        <v>0.9157</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8405</v>
+        <v>-1.7603</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7319</v>
+        <v>-0.7383</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.091</v>
+        <v>-0.1375</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6409</v>
+        <v>-0.6007</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2663</v>
+        <v>-0.1063</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0667</v>
+        <v>1.0533</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1996</v>
+        <v>-1.1596</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1117</v>
+        <v>0.1853</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R11" t="n">
         <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7959000000000001</v>
+        <v>0.476</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8207</v>
+        <v>0.3765</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0249</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6289</v>
+        <v>-1.26</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9383</v>
+        <v>-2.1981</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3039</v>
+        <v>-3.5637</v>
       </c>
       <c r="F12" t="n">
         <v>1.3656</v>
@@ -1390,10 +1390,10 @@
         <v>1.6676</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2823</v>
+        <v>0.4579</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8754</v>
+        <v>-0.1352</v>
       </c>
       <c r="U12" t="n">
         <v>0.5931</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.2117</v>
+        <v>-4.3544</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4761</v>
+        <v>-3.6927</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7356</v>
+        <v>-0.6617</v>
       </c>
       <c r="G13" t="n">
         <v>-5.3791</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5738</v>
+        <v>0.2835</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6019</v>
+        <v>0.1816</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0281</v>
+        <v>0.102</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.2882</v>
+        <v>20.5618</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2824000000000026</v>
+        <v>0.5559999999999987</v>
       </c>
       <c r="F14" t="n">
-        <v>20.0057</v>
+        <v>20.0058</v>
       </c>
       <c r="G14" t="n">
         <v>7.282799999999997</v>
@@ -1516,7 +1516,7 @@
         <v>6.629899999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6527000000000007</v>
+        <v>0.6527000000000003</v>
       </c>
       <c r="J14" t="n">
         <v>3.807599999999998</v>
@@ -1525,7 +1525,7 @@
         <v>4.308500000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5006999999999997</v>
+        <v>-0.5007000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>3.475299999999999</v>
@@ -1546,13 +1546,13 @@
         <v>12.9701</v>
       </c>
       <c r="S14" t="n">
-        <v>6.484899999999999</v>
+        <v>6.758599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0385</v>
+        <v>1.3121</v>
       </c>
       <c r="U14" t="n">
-        <v>5.4465</v>
+        <v>5.446499999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.8883</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.6633</v>
+        <v>4.4166</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6244</v>
+        <v>1.7223</v>
       </c>
       <c r="F15" t="n">
-        <v>3.0389</v>
+        <v>2.6942</v>
       </c>
       <c r="G15" t="n">
         <v>4.3963</v>
@@ -1624,13 +1624,13 @@
         <v>0.7411</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2137</v>
+        <v>-0.4604</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5807</v>
+        <v>-0.4828</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3671</v>
+        <v>0.0224</v>
       </c>
       <c r="V15" t="n">
         <v>2.5188</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. VALIENTE RODRIGUEZ</t>
+          <t>Á. CHAPARRO CARRASCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9606</v>
+        <v>1.8662</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1615</v>
+        <v>1.8662</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7992</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1601</v>
+        <v>1.8662</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1149</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2749</v>
+        <v>1.8662</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2746</v>
+        <v>1.8662</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.524</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7986</v>
+        <v>1.8662</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8855</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4092</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4763</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4823</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6817</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1131</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5686</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Á. CHAPARRO CARRASCO</t>
+          <t>S. VALIENTE RODRIGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8662</v>
+        <v>1.7905</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8662</v>
+        <v>-0.2303</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>2.0208</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8662</v>
+        <v>1.1601</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.1149</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8662</v>
+        <v>1.2749</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8662</v>
+        <v>0.2746</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.524</v>
       </c>
       <c r="L17" t="n">
-        <v>1.8662</v>
+        <v>0.7986</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>0.8855</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.4092</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.4763</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4823</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.8518</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.5049</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-0.347</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4026</v>
+        <v>-0.1827</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.135</v>
+        <v>-1.8412</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7324</v>
+        <v>1.6585</v>
       </c>
       <c r="G18" t="n">
         <v>0.6576</v>
@@ -1858,13 +1858,13 @@
         <v>0.3706</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5044</v>
+        <v>-0.2845</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.766</v>
+        <v>-0.4722</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2616</v>
+        <v>0.1878</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6063</v>
+        <v>-0.7042</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4472</v>
+        <v>-1.5451</v>
       </c>
       <c r="F19" t="n">
         <v>0.8409</v>
@@ -1936,10 +1936,10 @@
         <v>0.7411</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4676</v>
+        <v>-0.5655</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2561</v>
+        <v>-0.3541</v>
       </c>
       <c r="U19" t="n">
         <v>-0.2114</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7415</v>
+        <v>-0.8658</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1498</v>
+        <v>-1.9539</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4082</v>
+        <v>1.0882</v>
       </c>
       <c r="G20" t="n">
         <v>0.9345</v>
@@ -2014,13 +2014,13 @@
         <v>1.297</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7867</v>
+        <v>-0.9109</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9637</v>
+        <v>-0.7679</v>
       </c>
       <c r="U20" t="n">
-        <v>0.177</v>
+        <v>-0.143</v>
       </c>
       <c r="V20" t="n">
         <v>-1.26</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. NDOUR</t>
+          <t>M. MALINIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.594</v>
+        <v>-2.1103</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0099</v>
+        <v>-1.9804</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.1299</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0811</v>
+        <v>-1.1997</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7695</v>
+        <v>-1.3028</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3117</v>
+        <v>0.1031</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5684</v>
+        <v>-0.504</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6099</v>
+        <v>-0.5455</v>
       </c>
       <c r="L21" t="n">
         <v>0.0415</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5127</v>
+        <v>-0.6957</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1596</v>
+        <v>-0.7573</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3531</v>
+        <v>0.0616</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.7411</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1853</v>
+        <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5427</v>
+        <v>-0.3547</v>
       </c>
       <c r="T21" t="n">
-        <v>0.485</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0577</v>
+        <v>0.1952</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. MALINIC</t>
+          <t>B. NDOUR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4522</v>
+        <v>-2.2303</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.47</v>
+        <v>-1.6954</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0178</v>
+        <v>-0.5349</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.1997</v>
+        <v>-1.0811</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3028</v>
+        <v>-0.7695</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1031</v>
+        <v>-0.3117</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.504</v>
+        <v>-0.5684</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5455</v>
+        <v>-0.6099</v>
       </c>
       <c r="L22" t="n">
         <v>0.0415</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6957</v>
+        <v>-0.5127</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7573</v>
+        <v>-0.1596</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0616</v>
+        <v>-0.3531</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3706</v>
+        <v>0.1853</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6966</v>
+        <v>-0.0936</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0396</v>
+        <v>-0.2005</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3429</v>
+        <v>0.1069</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4271</v>
+        <v>-3.0102</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9389999999999999</v>
+        <v>-0.6452</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4881</v>
+        <v>-2.3649</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4967</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6715</v>
+        <v>-0.2546</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3619</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3096</v>
+        <v>-0.1865</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2589</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.7093</v>
+        <v>-3.782</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.1349</v>
+        <v>-4.3308</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4256</v>
+        <v>0.5487</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7114</v>
@@ -2326,13 +2326,13 @@
         <v>0.9264</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3134</v>
+        <v>-0.3861</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.332</v>
+        <v>-0.5279</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0186</v>
+        <v>0.1418</v>
       </c>
       <c r="V24" t="n">
         <v>0.3155</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.0768</v>
+        <v>-4.1495</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.9469</v>
+        <v>-3.1428</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1299</v>
+        <v>-1.0068</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7464</v>
@@ -2404,13 +2404,13 @@
         <v>0.9264</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4775</v>
+        <v>-0.5503</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2226</v>
+        <v>-0.4184</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2549</v>
+        <v>-0.1318</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.7214</v>
+        <v>-4.8926</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.1594</v>
+        <v>-3.3552</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.562</v>
+        <v>-1.5374</v>
       </c>
       <c r="G26" t="n">
         <v>-0.7193000000000001</v>
@@ -2482,13 +2482,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2783</v>
+        <v>-0.4495</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0584</v>
+        <v>-0.2543</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2199</v>
+        <v>-0.1952</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9444</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.0473</v>
+        <v>-6.4339</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.2658</v>
+        <v>-2.874</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.7815</v>
+        <v>-3.5599</v>
       </c>
       <c r="G27" t="n">
         <v>-4.2046</v>
@@ -2560,13 +2560,13 @@
         <v>1.297</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.9364</v>
+        <v>-1.3231</v>
       </c>
       <c r="T27" t="n">
-        <v>-1.2373</v>
+        <v>-0.8456</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6991000000000001</v>
+        <v>-0.4775</v>
       </c>
       <c r="V27" t="n">
         <v>-2.2033</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-20.2884</v>
+        <v>-20.2882</v>
       </c>
       <c r="E28" t="n">
         <v>-20.0058</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2827000000000006</v>
+        <v>-0.2824999999999998</v>
       </c>
       <c r="G28" t="n">
         <v>-7.2826</v>
@@ -2638,13 +2638,13 @@
         <v>8.3378</v>
       </c>
       <c r="S28" t="n">
-        <v>-6.485099999999999</v>
+        <v>-6.484999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>-5.4464</v>
+        <v>-5.4466</v>
       </c>
       <c r="U28" t="n">
-        <v>-1.0386</v>
+        <v>-1.0383</v>
       </c>
       <c r="V28" t="n">
         <v>-1.8884</v>
